--- a/ig/main/ValueSet-1.2.250.1.213.1.1.5.585.xlsx
+++ b/ig/main/ValueSet-1.2.250.1.213.1.1.5.585.xlsx
@@ -69,7 +69,7 @@
     <t>Publisher</t>
   </si>
   <si>
-    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
+    <t>Agence du Numérique en Santé(ANS) -2 - 10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Description</t>
@@ -6288,7 +6288,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>urn:oid:2.16.840.1.113883.6.43.1</t>
+    <t>http://terminology.hl7.org/CodeSystem/icd-o-3</t>
   </si>
 </sst>
 </file>
